--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31575,6 +31575,81 @@
         <v>349.44</v>
       </c>
       <c r="W415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>342.33</v>
+      </c>
+      <c r="C416" t="n">
+        <v>331.71</v>
+      </c>
+      <c r="D416" t="n">
+        <v>330.7</v>
+      </c>
+      <c r="E416" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F416" t="n">
+        <v>324.93</v>
+      </c>
+      <c r="G416" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="H416" t="n">
+        <v>325.44</v>
+      </c>
+      <c r="I416" t="n">
+        <v>334.04</v>
+      </c>
+      <c r="J416" t="n">
+        <v>338.21</v>
+      </c>
+      <c r="K416" t="n">
+        <v>339.85</v>
+      </c>
+      <c r="L416" t="n">
+        <v>340.74</v>
+      </c>
+      <c r="M416" t="n">
+        <v>348.94</v>
+      </c>
+      <c r="N416" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="O416" t="n">
+        <v>350.54</v>
+      </c>
+      <c r="P416" t="n">
+        <v>361.55</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>357.99</v>
+      </c>
+      <c r="R416" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="S416" t="n">
+        <v>343.27</v>
+      </c>
+      <c r="T416" t="n">
+        <v>344.22</v>
+      </c>
+      <c r="U416" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="V416" t="n">
+        <v>350.17</v>
+      </c>
+      <c r="W416" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31591,7 +31666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B417"/>
+  <dimension ref="A1:B418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35764,6 +35839,16 @@
       </c>
       <c r="B417" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -35932,28 +36017,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1859250585111105</v>
+        <v>0.1843426594274248</v>
       </c>
       <c r="J2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1137642467464661</v>
+        <v>0.1125009095965158</v>
       </c>
       <c r="M2" t="n">
-        <v>3.159296520294163</v>
+        <v>3.158775236788547</v>
       </c>
       <c r="N2" t="n">
-        <v>15.24409899526026</v>
+        <v>15.23082933042791</v>
       </c>
       <c r="O2" t="n">
-        <v>3.904369218613969</v>
+        <v>3.902669513349536</v>
       </c>
       <c r="P2" t="n">
-        <v>340.4569874675587</v>
+        <v>340.4732267444323</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36010,28 +36095,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2234854854819171</v>
+        <v>0.2212882617916373</v>
       </c>
       <c r="J3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.135667334212444</v>
+        <v>0.1337754199664658</v>
       </c>
       <c r="M3" t="n">
-        <v>3.424735580999537</v>
+        <v>3.426227336732855</v>
       </c>
       <c r="N3" t="n">
-        <v>18.01302766938275</v>
+        <v>18.01486063411363</v>
       </c>
       <c r="O3" t="n">
-        <v>4.24417573497879</v>
+        <v>4.244391668321107</v>
       </c>
       <c r="P3" t="n">
-        <v>330.0415362969533</v>
+        <v>330.0640851749372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36088,28 +36173,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2349266092643272</v>
+        <v>0.23359828338918</v>
       </c>
       <c r="J4" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1412854914852449</v>
+        <v>0.1405388223752581</v>
       </c>
       <c r="M4" t="n">
-        <v>3.485068698530956</v>
+        <v>3.484037632224518</v>
       </c>
       <c r="N4" t="n">
-        <v>18.98882493312693</v>
+        <v>18.95960214785187</v>
       </c>
       <c r="O4" t="n">
-        <v>4.357616886915018</v>
+        <v>4.354262526289827</v>
       </c>
       <c r="P4" t="n">
-        <v>327.0014928663138</v>
+        <v>327.0151247319332</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36166,28 +36251,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1797852488220567</v>
+        <v>0.1786466511300452</v>
       </c>
       <c r="J5" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K5" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07165118599638642</v>
+        <v>0.07117538669585766</v>
       </c>
       <c r="M5" t="n">
-        <v>3.857386915361744</v>
+        <v>3.853725740507601</v>
       </c>
       <c r="N5" t="n">
-        <v>23.70709555312121</v>
+        <v>23.66211772047101</v>
       </c>
       <c r="O5" t="n">
-        <v>4.868993279223253</v>
+        <v>4.864372284321072</v>
       </c>
       <c r="P5" t="n">
-        <v>325.5313018611633</v>
+        <v>325.5429866525405</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36244,28 +36329,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1825535764604846</v>
+        <v>0.1809294320400837</v>
       </c>
       <c r="J6" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K6" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07220346953156875</v>
+        <v>0.07134737334038499</v>
       </c>
       <c r="M6" t="n">
-        <v>4.062542167886436</v>
+        <v>4.06090109665563</v>
       </c>
       <c r="N6" t="n">
-        <v>24.24140595396806</v>
+        <v>24.20771032302709</v>
       </c>
       <c r="O6" t="n">
-        <v>4.923556230405829</v>
+        <v>4.920133161107237</v>
       </c>
       <c r="P6" t="n">
-        <v>323.2322639830123</v>
+        <v>323.2489316689315</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36322,28 +36407,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2227556745537794</v>
+        <v>0.2210621201789734</v>
       </c>
       <c r="J7" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K7" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08822658939887029</v>
+        <v>0.08741380100121832</v>
       </c>
       <c r="M7" t="n">
-        <v>4.442882046997982</v>
+        <v>4.441741733060563</v>
       </c>
       <c r="N7" t="n">
-        <v>29.02868884274492</v>
+        <v>28.98561539506743</v>
       </c>
       <c r="O7" t="n">
-        <v>5.387827840859888</v>
+        <v>5.38382906443615</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0576558236959</v>
+        <v>323.0750358251613</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36400,28 +36485,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.15032318214129</v>
+        <v>0.1478309997184671</v>
       </c>
       <c r="J8" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K8" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04801487755850087</v>
+        <v>0.04667591044107444</v>
       </c>
       <c r="M8" t="n">
-        <v>4.001658424909266</v>
+        <v>4.006129813859207</v>
       </c>
       <c r="N8" t="n">
-        <v>25.36230333900896</v>
+        <v>25.35938802697731</v>
       </c>
       <c r="O8" t="n">
-        <v>5.036100012808419</v>
+        <v>5.035810563055098</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3265659304765</v>
+        <v>326.3521418049834</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36478,28 +36563,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2232732866416096</v>
+        <v>0.2238185090650563</v>
       </c>
       <c r="J9" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K9" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1226604906480215</v>
+        <v>0.1238258031171416</v>
       </c>
       <c r="M9" t="n">
-        <v>3.442071263324777</v>
+        <v>3.435780990776411</v>
       </c>
       <c r="N9" t="n">
-        <v>20.184544640676</v>
+        <v>20.13869266877787</v>
       </c>
       <c r="O9" t="n">
-        <v>4.492721295682161</v>
+        <v>4.487615476929577</v>
       </c>
       <c r="P9" t="n">
-        <v>326.9411971848739</v>
+        <v>326.9356018720459</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36556,28 +36641,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2111565644990347</v>
+        <v>0.2120054373621204</v>
       </c>
       <c r="J10" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K10" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06723946544609605</v>
+        <v>0.06811497387904974</v>
       </c>
       <c r="M10" t="n">
-        <v>4.491278024802913</v>
+        <v>4.48279308108534</v>
       </c>
       <c r="N10" t="n">
-        <v>35.01366087457725</v>
+        <v>34.93604270510397</v>
       </c>
       <c r="O10" t="n">
-        <v>5.917234225090067</v>
+        <v>5.910671933469491</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8422994741923</v>
+        <v>330.8335879667121</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36634,28 +36719,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1458433623622382</v>
+        <v>0.1456642153977079</v>
       </c>
       <c r="J11" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K11" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0240950370027091</v>
+        <v>0.02417937563751638</v>
       </c>
       <c r="M11" t="n">
-        <v>5.457717077135691</v>
+        <v>5.445642664087157</v>
       </c>
       <c r="N11" t="n">
-        <v>48.76808488062396</v>
+        <v>48.65087215001299</v>
       </c>
       <c r="O11" t="n">
-        <v>6.98341498699769</v>
+        <v>6.975017716824309</v>
       </c>
       <c r="P11" t="n">
-        <v>336.2796838083827</v>
+        <v>336.2815222934956</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36712,28 +36797,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1489908726250141</v>
+        <v>0.1483133992543035</v>
       </c>
       <c r="J12" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K12" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02782875871437418</v>
+        <v>0.02774317490779799</v>
       </c>
       <c r="M12" t="n">
-        <v>5.235997767061749</v>
+        <v>5.227876993787913</v>
       </c>
       <c r="N12" t="n">
-        <v>43.89860277789215</v>
+        <v>43.79712369954983</v>
       </c>
       <c r="O12" t="n">
-        <v>6.625602069087167</v>
+        <v>6.617939535803409</v>
       </c>
       <c r="P12" t="n">
-        <v>338.0667385416806</v>
+        <v>338.073691072022</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36790,28 +36875,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1727379686358515</v>
+        <v>0.172904762997037</v>
       </c>
       <c r="J13" t="n">
+        <v>415</v>
+      </c>
+      <c r="K13" t="n">
         <v>414</v>
       </c>
-      <c r="K13" t="n">
-        <v>413</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.04159834938813389</v>
+        <v>0.04191703612885722</v>
       </c>
       <c r="M13" t="n">
-        <v>4.876476996600418</v>
+        <v>4.86521679341578</v>
       </c>
       <c r="N13" t="n">
-        <v>39.00279863191609</v>
+        <v>38.90885041303796</v>
       </c>
       <c r="O13" t="n">
-        <v>6.245222064259693</v>
+        <v>6.23769592181584</v>
       </c>
       <c r="P13" t="n">
-        <v>343.9569742007046</v>
+        <v>343.955263728943</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36868,28 +36953,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07627850639985025</v>
+        <v>0.0760865803741983</v>
       </c>
       <c r="J14" t="n">
+        <v>415</v>
+      </c>
+      <c r="K14" t="n">
         <v>414</v>
       </c>
-      <c r="K14" t="n">
-        <v>413</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.00899550066465904</v>
+        <v>0.009004355028355948</v>
       </c>
       <c r="M14" t="n">
-        <v>4.752736947655658</v>
+        <v>4.742544537102031</v>
       </c>
       <c r="N14" t="n">
-        <v>36.36665423125626</v>
+        <v>36.27915823094896</v>
       </c>
       <c r="O14" t="n">
-        <v>6.030477114727844</v>
+        <v>6.023218261938459</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1281903641888</v>
+        <v>345.1301585605045</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36946,28 +37031,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06213555899742979</v>
+        <v>0.06163115563218204</v>
       </c>
       <c r="J15" t="n">
+        <v>415</v>
+      </c>
+      <c r="K15" t="n">
         <v>414</v>
       </c>
-      <c r="K15" t="n">
-        <v>413</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.007244940293750446</v>
+        <v>0.007170942344893017</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2749345033205</v>
+        <v>4.267216683144931</v>
       </c>
       <c r="N15" t="n">
-        <v>30.01486662783258</v>
+        <v>29.94475786798235</v>
       </c>
       <c r="O15" t="n">
-        <v>5.478582538196589</v>
+        <v>5.472180357771695</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8641640320741</v>
+        <v>349.8693366752411</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37024,28 +37109,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01893032025023297</v>
+        <v>-0.01823884116301157</v>
       </c>
       <c r="J16" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K16" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0008912857050692446</v>
+        <v>0.0008322631845844031</v>
       </c>
       <c r="M16" t="n">
-        <v>3.834778048947695</v>
+        <v>3.828424052980237</v>
       </c>
       <c r="N16" t="n">
-        <v>22.74019391197051</v>
+        <v>22.68987860960645</v>
       </c>
       <c r="O16" t="n">
-        <v>4.768667938950092</v>
+        <v>4.76338940352418</v>
       </c>
       <c r="P16" t="n">
-        <v>360.6906355007882</v>
+        <v>360.6835392376107</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37102,28 +37187,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.004748494300658644</v>
+        <v>-0.002679253690041608</v>
       </c>
       <c r="J17" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K17" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L17" t="n">
-        <v>5.018667557665779e-05</v>
+        <v>1.604937528998374e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.16725484570928</v>
+        <v>4.166009059732705</v>
       </c>
       <c r="N17" t="n">
-        <v>25.4322071900066</v>
+        <v>25.41104610063531</v>
       </c>
       <c r="O17" t="n">
-        <v>5.043035513458794</v>
+        <v>5.040937026053323</v>
       </c>
       <c r="P17" t="n">
-        <v>354.0151500234438</v>
+        <v>353.9939145642347</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37180,28 +37265,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05176466902650114</v>
+        <v>0.05402530587734983</v>
       </c>
       <c r="J18" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K18" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01004211184542814</v>
+        <v>0.01095931629510538</v>
       </c>
       <c r="M18" t="n">
-        <v>3.261527456339195</v>
+        <v>3.264697312925925</v>
       </c>
       <c r="N18" t="n">
-        <v>14.95343561873716</v>
+        <v>14.96528995619681</v>
       </c>
       <c r="O18" t="n">
-        <v>3.866967237867055</v>
+        <v>3.868499703528075</v>
       </c>
       <c r="P18" t="n">
-        <v>343.8956324071979</v>
+        <v>343.8724327554094</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37258,28 +37343,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07458886937875708</v>
+        <v>0.07764217113660457</v>
       </c>
       <c r="J19" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K19" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0211012479385454</v>
+        <v>0.02282512123154301</v>
       </c>
       <c r="M19" t="n">
-        <v>3.161740058417283</v>
+        <v>3.168715213901661</v>
       </c>
       <c r="N19" t="n">
-        <v>14.67567900160038</v>
+        <v>14.72800772939056</v>
       </c>
       <c r="O19" t="n">
-        <v>3.83088488493199</v>
+        <v>3.837708656137222</v>
       </c>
       <c r="P19" t="n">
-        <v>335.2160977301826</v>
+        <v>335.1848094416231</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37336,28 +37421,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.179990843717781</v>
+        <v>0.1825814899208764</v>
       </c>
       <c r="J20" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K20" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1117116223474383</v>
+        <v>0.1147537853527882</v>
       </c>
       <c r="M20" t="n">
-        <v>3.144523473558973</v>
+        <v>3.150082473557602</v>
       </c>
       <c r="N20" t="n">
-        <v>14.64795400617873</v>
+        <v>14.67574008943205</v>
       </c>
       <c r="O20" t="n">
-        <v>3.827264559209191</v>
+        <v>3.830892857994341</v>
       </c>
       <c r="P20" t="n">
-        <v>334.2391709312286</v>
+        <v>334.2126236416428</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37414,28 +37499,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3698662430898613</v>
+        <v>0.3727060056907907</v>
       </c>
       <c r="J21" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K21" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3286074941293151</v>
+        <v>0.3322694757243471</v>
       </c>
       <c r="M21" t="n">
-        <v>3.257031663085399</v>
+        <v>3.262787549131125</v>
       </c>
       <c r="N21" t="n">
-        <v>15.89311181764606</v>
+        <v>15.93063274204602</v>
       </c>
       <c r="O21" t="n">
-        <v>3.986616587740293</v>
+        <v>3.991319674248859</v>
       </c>
       <c r="P21" t="n">
-        <v>331.25427266399</v>
+        <v>331.2251725884832</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37492,28 +37577,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3091026950442026</v>
+        <v>0.3121894852112141</v>
       </c>
       <c r="J22" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K22" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2242700131205519</v>
+        <v>0.227970268184577</v>
       </c>
       <c r="M22" t="n">
-        <v>3.560366141888422</v>
+        <v>3.565529130626205</v>
       </c>
       <c r="N22" t="n">
-        <v>18.70800126176514</v>
+        <v>18.75220450601031</v>
       </c>
       <c r="O22" t="n">
-        <v>4.325274703618851</v>
+        <v>4.330381565868106</v>
       </c>
       <c r="P22" t="n">
-        <v>335.7277746165251</v>
+        <v>335.6960966152611</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37551,7 +37636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86073,6 +86158,123 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-38.27446978061607,178.33040446228358</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-38.27516670187218,178.33060944528142</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-38.27583017235112,178.33091545499747</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-38.27649910090445,178.33120495925195</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-38.2771689056356,178.33148748229107</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-38.27782505024324,178.33180306874561</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-38.278489691189485,178.3320950249359</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-38.27912744170879,178.33248197950573</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-38.279784178025466,178.33282366936095</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-38.280438708792836,178.33318629779245</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-38.28107086168767,178.33359974546977</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-38.28167131649415,178.33408596095887</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-38.28226577528086,178.33458404518217</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-38.28281769364233,178.3351434609575</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-38.283326566464986,178.33576308322094</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-38.283821701023506,178.33639631808464</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-38.284342534146205,178.3370122116643</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-38.28486667136804,178.33761536120423</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>-38.28536241085809,178.33826194799857</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>-38.28578744036757,178.33898958004232</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>-38.28612502174871,178.33978630815227</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W416"/>
+  <dimension ref="A1:W419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31650,6 +31650,231 @@
         <v>350.17</v>
       </c>
       <c r="W416" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="C417" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="D417" t="n">
+        <v>331.02</v>
+      </c>
+      <c r="E417" t="n">
+        <v>329.47</v>
+      </c>
+      <c r="F417" t="n">
+        <v>326.74</v>
+      </c>
+      <c r="G417" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="H417" t="n">
+        <v>326.23</v>
+      </c>
+      <c r="I417" t="n">
+        <v>334.47</v>
+      </c>
+      <c r="J417" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="K417" t="n">
+        <v>340.27</v>
+      </c>
+      <c r="L417" t="n">
+        <v>340.73</v>
+      </c>
+      <c r="M417" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="N417" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="O417" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="P417" t="n">
+        <v>362.28</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="R417" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="S417" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="T417" t="n">
+        <v>344.61</v>
+      </c>
+      <c r="U417" t="n">
+        <v>347.38</v>
+      </c>
+      <c r="V417" t="n">
+        <v>351.14</v>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="C418" t="n">
+        <v>332.24</v>
+      </c>
+      <c r="D418" t="n">
+        <v>331.06</v>
+      </c>
+      <c r="E418" t="n">
+        <v>330.38</v>
+      </c>
+      <c r="F418" t="n">
+        <v>328.24</v>
+      </c>
+      <c r="G418" t="n">
+        <v>327.41</v>
+      </c>
+      <c r="H418" t="n">
+        <v>326.22</v>
+      </c>
+      <c r="I418" t="n">
+        <v>334.04</v>
+      </c>
+      <c r="J418" t="n">
+        <v>338.9</v>
+      </c>
+      <c r="K418" t="n">
+        <v>340.15</v>
+      </c>
+      <c r="L418" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="M418" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="N418" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="O418" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="P418" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="R418" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="S418" t="n">
+        <v>343.01</v>
+      </c>
+      <c r="T418" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="U418" t="n">
+        <v>346.91</v>
+      </c>
+      <c r="V418" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:53:53+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>342.64</v>
+      </c>
+      <c r="C419" t="n">
+        <v>332.82</v>
+      </c>
+      <c r="D419" t="n">
+        <v>331.69</v>
+      </c>
+      <c r="E419" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="F419" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="G419" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="H419" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="I419" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="J419" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="K419" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="L419" t="n">
+        <v>340.06</v>
+      </c>
+      <c r="M419" t="n">
+        <v>349.72</v>
+      </c>
+      <c r="N419" t="n">
+        <v>348.19</v>
+      </c>
+      <c r="O419" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="P419" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="R419" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="S419" t="n">
+        <v>342.25</v>
+      </c>
+      <c r="T419" t="n">
+        <v>343.32</v>
+      </c>
+      <c r="U419" t="n">
+        <v>345.83</v>
+      </c>
+      <c r="V419" t="n">
+        <v>349.41</v>
+      </c>
+      <c r="W419" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31666,7 +31891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B418"/>
+  <dimension ref="A1:B421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35849,6 +36074,36 @@
       </c>
       <c r="B418" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -36017,28 +36272,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1843426594274248</v>
+        <v>0.1799866732043864</v>
       </c>
       <c r="J2" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1125009095965158</v>
+        <v>0.1091568438247894</v>
       </c>
       <c r="M2" t="n">
-        <v>3.158775236788547</v>
+        <v>3.155703632567634</v>
       </c>
       <c r="N2" t="n">
-        <v>15.23082933042791</v>
+        <v>15.18226953633944</v>
       </c>
       <c r="O2" t="n">
-        <v>3.902669513349536</v>
+        <v>3.896443190441693</v>
       </c>
       <c r="P2" t="n">
-        <v>340.4732267444323</v>
+        <v>340.5180185569606</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36095,28 +36350,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2212882617916373</v>
+        <v>0.2159357069959709</v>
       </c>
       <c r="J3" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1337754199664658</v>
+        <v>0.129637913542499</v>
       </c>
       <c r="M3" t="n">
-        <v>3.426227336732855</v>
+        <v>3.42609864840288</v>
       </c>
       <c r="N3" t="n">
-        <v>18.01486063411363</v>
+        <v>17.97722184283602</v>
       </c>
       <c r="O3" t="n">
-        <v>4.244391668321107</v>
+        <v>4.239955405760303</v>
       </c>
       <c r="P3" t="n">
-        <v>330.0640851749372</v>
+        <v>330.1191203361214</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36173,28 +36428,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.23359828338918</v>
+        <v>0.2305395705736926</v>
       </c>
       <c r="J4" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1405388223752581</v>
+        <v>0.139326300418488</v>
       </c>
       <c r="M4" t="n">
-        <v>3.484037632224518</v>
+        <v>3.475873355384862</v>
       </c>
       <c r="N4" t="n">
-        <v>18.95960214785187</v>
+        <v>18.85393937955913</v>
       </c>
       <c r="O4" t="n">
-        <v>4.354262526289827</v>
+        <v>4.342112317704268</v>
       </c>
       <c r="P4" t="n">
-        <v>327.0151247319332</v>
+        <v>327.046572219354</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36251,28 +36506,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1786466511300452</v>
+        <v>0.1784322875558835</v>
       </c>
       <c r="J5" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07117538669585766</v>
+        <v>0.07220018102537662</v>
       </c>
       <c r="M5" t="n">
-        <v>3.853725740507601</v>
+        <v>3.829312060855708</v>
       </c>
       <c r="N5" t="n">
-        <v>23.66211772047101</v>
+        <v>23.4946296474305</v>
       </c>
       <c r="O5" t="n">
-        <v>4.864372284321072</v>
+        <v>4.847125916193069</v>
       </c>
       <c r="P5" t="n">
-        <v>325.5429866525405</v>
+        <v>325.5451825022535</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36329,28 +36584,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1809294320400837</v>
+        <v>0.1803875830604989</v>
       </c>
       <c r="J6" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07134737334038499</v>
+        <v>0.07212699428555702</v>
       </c>
       <c r="M6" t="n">
-        <v>4.06090109665563</v>
+        <v>4.035931064246518</v>
       </c>
       <c r="N6" t="n">
-        <v>24.20771032302709</v>
+        <v>24.03862956078897</v>
       </c>
       <c r="O6" t="n">
-        <v>4.920133161107237</v>
+        <v>4.902920513407184</v>
       </c>
       <c r="P6" t="n">
-        <v>323.2489316689315</v>
+        <v>323.2544941118576</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36407,28 +36662,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2210621201789734</v>
+        <v>0.2185036050020338</v>
       </c>
       <c r="J7" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K7" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08741380100121832</v>
+        <v>0.08692775825086319</v>
       </c>
       <c r="M7" t="n">
-        <v>4.441741733060563</v>
+        <v>4.424154661648511</v>
       </c>
       <c r="N7" t="n">
-        <v>28.98561539506743</v>
+        <v>28.79848180372272</v>
       </c>
       <c r="O7" t="n">
-        <v>5.38382906443615</v>
+        <v>5.36642169454868</v>
       </c>
       <c r="P7" t="n">
-        <v>323.0750358251613</v>
+        <v>323.1013434669053</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36485,28 +36740,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1478309997184671</v>
+        <v>0.141632173078818</v>
       </c>
       <c r="J8" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K8" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04667591044107444</v>
+        <v>0.04354903359040418</v>
       </c>
       <c r="M8" t="n">
-        <v>4.006129813859207</v>
+        <v>4.012137063288159</v>
       </c>
       <c r="N8" t="n">
-        <v>25.35938802697731</v>
+        <v>25.29960528905145</v>
       </c>
       <c r="O8" t="n">
-        <v>5.035810563055098</v>
+        <v>5.029871299452049</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3521418049834</v>
+        <v>326.415884792824</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36563,28 +36818,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2238185090650563</v>
+        <v>0.225326393477696</v>
       </c>
       <c r="J9" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K9" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1238258031171416</v>
+        <v>0.1272179966926806</v>
       </c>
       <c r="M9" t="n">
-        <v>3.435780990776411</v>
+        <v>3.416613137028984</v>
       </c>
       <c r="N9" t="n">
-        <v>20.13869266877787</v>
+        <v>20.0026290544356</v>
       </c>
       <c r="O9" t="n">
-        <v>4.487615476929577</v>
+        <v>4.47242988256223</v>
       </c>
       <c r="P9" t="n">
-        <v>326.9356018720459</v>
+        <v>326.9201033326889</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36641,28 +36896,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2120054373621204</v>
+        <v>0.2152151012044038</v>
       </c>
       <c r="J10" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K10" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06811497387904974</v>
+        <v>0.0711589450762834</v>
       </c>
       <c r="M10" t="n">
-        <v>4.48279308108534</v>
+        <v>4.459494692459558</v>
       </c>
       <c r="N10" t="n">
-        <v>34.93604270510397</v>
+        <v>34.71867201439922</v>
       </c>
       <c r="O10" t="n">
-        <v>5.910671933469491</v>
+        <v>5.892255257064074</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8335879667121</v>
+        <v>330.8005880892281</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36719,28 +36974,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1456642153977079</v>
+        <v>0.1453132334075272</v>
       </c>
       <c r="J11" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K11" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02417937563751638</v>
+        <v>0.02448922653395103</v>
       </c>
       <c r="M11" t="n">
-        <v>5.445642664087157</v>
+        <v>5.40893798921046</v>
       </c>
       <c r="N11" t="n">
-        <v>48.65087215001299</v>
+        <v>48.30288317634973</v>
       </c>
       <c r="O11" t="n">
-        <v>6.975017716824309</v>
+        <v>6.950027566589196</v>
       </c>
       <c r="P11" t="n">
-        <v>336.2815222934956</v>
+        <v>336.2851367723118</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36797,28 +37052,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1483133992543035</v>
+        <v>0.1456719807888098</v>
       </c>
       <c r="J12" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K12" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02774317490779799</v>
+        <v>0.02724676475816434</v>
       </c>
       <c r="M12" t="n">
-        <v>5.227876993787913</v>
+        <v>5.207692248679277</v>
       </c>
       <c r="N12" t="n">
-        <v>43.79712369954983</v>
+        <v>43.50563509614486</v>
       </c>
       <c r="O12" t="n">
-        <v>6.617939535803409</v>
+        <v>6.595880160838647</v>
       </c>
       <c r="P12" t="n">
-        <v>338.073691072022</v>
+        <v>338.1008564158026</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36875,28 +37130,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.172904762997037</v>
+        <v>0.1746159569111581</v>
       </c>
       <c r="J13" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K13" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04191703612885722</v>
+        <v>0.04344255585056411</v>
       </c>
       <c r="M13" t="n">
-        <v>4.86521679341578</v>
+        <v>4.835526852341088</v>
       </c>
       <c r="N13" t="n">
-        <v>38.90885041303796</v>
+        <v>38.63833268940625</v>
       </c>
       <c r="O13" t="n">
-        <v>6.23769592181584</v>
+        <v>6.215973993623706</v>
       </c>
       <c r="P13" t="n">
-        <v>343.955263728943</v>
+        <v>343.9376806556459</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36953,28 +37208,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0760865803741983</v>
+        <v>0.07716717231756907</v>
       </c>
       <c r="J14" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K14" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009004355028355948</v>
+        <v>0.009424046183649115</v>
       </c>
       <c r="M14" t="n">
-        <v>4.742544537102031</v>
+        <v>4.711471846389621</v>
       </c>
       <c r="N14" t="n">
-        <v>36.27915823094896</v>
+        <v>36.02221232476324</v>
       </c>
       <c r="O14" t="n">
-        <v>6.023218261938459</v>
+        <v>6.001850741626556</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1301585605045</v>
+        <v>345.1190514473177</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37031,28 +37286,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06163115563218204</v>
+        <v>0.06182855156051358</v>
       </c>
       <c r="J15" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K15" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007170942344893017</v>
+        <v>0.007345823270332841</v>
       </c>
       <c r="M15" t="n">
-        <v>4.267216683144931</v>
+        <v>4.237997993626879</v>
       </c>
       <c r="N15" t="n">
-        <v>29.94475786798235</v>
+        <v>29.72969659324261</v>
       </c>
       <c r="O15" t="n">
-        <v>5.472180357771695</v>
+        <v>5.452494529409691</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8693366752411</v>
+        <v>349.8673061957436</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37109,28 +37364,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01823884116301157</v>
+        <v>-0.01506601961097869</v>
       </c>
       <c r="J16" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K16" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0008322631845844031</v>
+        <v>0.0005774709533497013</v>
       </c>
       <c r="M16" t="n">
-        <v>3.828424052980237</v>
+        <v>3.814110330363254</v>
       </c>
       <c r="N16" t="n">
-        <v>22.68987860960645</v>
+        <v>22.55909990851417</v>
       </c>
       <c r="O16" t="n">
-        <v>4.76338940352418</v>
+        <v>4.749642082148314</v>
       </c>
       <c r="P16" t="n">
-        <v>360.6835392376107</v>
+        <v>360.6509140511771</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37187,28 +37442,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.002679253690041608</v>
+        <v>0.006129222252021204</v>
       </c>
       <c r="J17" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K17" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L17" t="n">
-        <v>1.604937528998374e-05</v>
+        <v>8.467436316128563e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.166009059732705</v>
+        <v>4.173465183835679</v>
       </c>
       <c r="N17" t="n">
-        <v>25.41104610063531</v>
+        <v>25.47579496818386</v>
       </c>
       <c r="O17" t="n">
-        <v>5.040937026053323</v>
+        <v>5.047355244896465</v>
       </c>
       <c r="P17" t="n">
-        <v>353.9939145642347</v>
+        <v>353.9033348933417</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37265,28 +37520,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05402530587734983</v>
+        <v>0.06200689095699856</v>
       </c>
       <c r="J18" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K18" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01095931629510538</v>
+        <v>0.01444845569459419</v>
       </c>
       <c r="M18" t="n">
-        <v>3.264697312925925</v>
+        <v>3.279779918121055</v>
       </c>
       <c r="N18" t="n">
-        <v>14.96528995619681</v>
+        <v>15.06064406106815</v>
       </c>
       <c r="O18" t="n">
-        <v>3.868499703528075</v>
+        <v>3.880804563627</v>
       </c>
       <c r="P18" t="n">
-        <v>343.8724327554094</v>
+        <v>343.7903610104614</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37343,28 +37598,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07764217113660457</v>
+        <v>0.086050965794028</v>
       </c>
       <c r="J19" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K19" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02282512123154301</v>
+        <v>0.02795589727266679</v>
       </c>
       <c r="M19" t="n">
-        <v>3.168715213901661</v>
+        <v>3.185976037905985</v>
       </c>
       <c r="N19" t="n">
-        <v>14.72800772939056</v>
+        <v>14.8502428328242</v>
       </c>
       <c r="O19" t="n">
-        <v>3.837708656137222</v>
+        <v>3.853601280986942</v>
       </c>
       <c r="P19" t="n">
-        <v>335.1848094416231</v>
+        <v>335.0984780925565</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37421,28 +37676,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1825814899208764</v>
+        <v>0.1899573370730178</v>
       </c>
       <c r="J20" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K20" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147537853527882</v>
+        <v>0.123680253846873</v>
       </c>
       <c r="M20" t="n">
-        <v>3.150082473557602</v>
+        <v>3.164525105058069</v>
       </c>
       <c r="N20" t="n">
-        <v>14.67574008943205</v>
+        <v>14.74632831424647</v>
       </c>
       <c r="O20" t="n">
-        <v>3.830892857994341</v>
+        <v>3.840094831413213</v>
       </c>
       <c r="P20" t="n">
-        <v>334.2126236416428</v>
+        <v>334.1368986281275</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37499,28 +37754,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3727060056907907</v>
+        <v>0.3807444654427254</v>
       </c>
       <c r="J21" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K21" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3322694757243471</v>
+        <v>0.3428608712107286</v>
       </c>
       <c r="M21" t="n">
-        <v>3.262787549131125</v>
+        <v>3.277656735386091</v>
       </c>
       <c r="N21" t="n">
-        <v>15.93063274204602</v>
+        <v>16.02566739621572</v>
       </c>
       <c r="O21" t="n">
-        <v>3.991319674248859</v>
+        <v>4.003207138809548</v>
       </c>
       <c r="P21" t="n">
-        <v>331.2251725884832</v>
+        <v>331.1426456171201</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37577,28 +37832,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3121894852112141</v>
+        <v>0.3214839955044986</v>
       </c>
       <c r="J22" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K22" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L22" t="n">
-        <v>0.227970268184577</v>
+        <v>0.2390143464862075</v>
       </c>
       <c r="M22" t="n">
-        <v>3.565529130626205</v>
+        <v>3.581694579784541</v>
       </c>
       <c r="N22" t="n">
-        <v>18.75220450601031</v>
+        <v>18.8963069111092</v>
       </c>
       <c r="O22" t="n">
-        <v>4.330381565868106</v>
+        <v>4.346988257530632</v>
       </c>
       <c r="P22" t="n">
-        <v>335.6960966152611</v>
+        <v>335.6005348086684</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37636,7 +37891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W416"/>
+  <dimension ref="A1:W419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86275,6 +86530,357 @@
         </is>
       </c>
     </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-38.274468388530074,178.33040866735442</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-38.275164926955505,178.33061480679314</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-38.275829058670865,178.33091881910903</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-38.276494402537246,178.33121915170778</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-38.27716267446549,178.33150654692525</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-38.27782017492526,178.33181852498</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-38.27848710519607,178.33210341442103</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-38.27912603412996,178.33248654596608</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-38.27978162161419,178.33283133567738</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-38.280437018063,178.33319057986037</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-38.28107090485663,178.33359964545178</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-38.28166760645264,178.33409323779804</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-38.28226106875669,178.3345918246166</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-38.28281294284129,178.3351511970048</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-38.28332201374155,178.33576907777422</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-38.283811234997394,178.33640728120272</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-38.28433620521049,178.33701896386938</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-38.284864466012046,178.33761787773835</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>-38.28535971014953,178.33826478332003</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>-38.285783343457055,178.338992882036</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>-38.286117364020676,178.3397915964865</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:27+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-38.27447033745045,178.3304027802552</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-38.27516485735092,178.33061501704847</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-38.27582891946082,178.33091923962297</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-38.276491235488834,178.3312287184732</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-38.277157510510186,178.33152234634312</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-38.277819340110334,178.33182117159524</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-38.27848713793018,178.33210330822504</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-38.27912744170879,178.33248197950573</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-38.27978176169153,178.33283091560529</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-38.28043750112868,178.33318935641242</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-38.281073581331704,178.33359344433617</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-38.28166658130955,178.3340952485035</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-38.282259810035036,178.33459390516282</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-38.28281067792435,178.33515488512</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-38.283320891152165,178.33577055588313</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-38.28380783873708,178.33641083877018</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-38.28433462297651,178.33702065192045</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-38.28486840892121,178.33761337848028</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
+        <is>
+          <t>-38.285361095128295,178.33826332930906</t>
+        </is>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>-38.28578690928659,178.33899000807858</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>-38.28612154814013,178.33978870698442</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-15 21:53:53+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-38.27446870174943,178.3304077212135</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-38.275162838817934,178.3306211144536</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-38.27582672690252,178.33092586271724</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-38.276489738971215,178.3312332390324</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-38.277157235099175,178.33152318897868</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-38.27781944028812,178.33182085400142</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-38.278487727143904,178.33210139669683</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-38.27912927483443,178.33247603248725</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-38.279783792812836,178.33282482455937</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-38.280440037223315,178.33318293331035</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-38.281073797176454,178.3335929442462</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-38.28166750881998,178.33409342929383</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-38.28225816822412,178.33459661891868</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-38.28281084364999,178.33515461525792</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-38.28332213847369,178.33576891353988</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-38.28380721493416,178.3364114922009</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-38.284337374687766,178.3370177161794</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-38.284873487922646,178.33760758282511</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>-38.28536864326228,178.3382554049482</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>-38.28579510310747,178.3389834040903</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>-38.286131021617976,178.33978216471445</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0253/nzd0253.xlsx
+++ b/data/nzd0253/nzd0253.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W419"/>
+  <dimension ref="A1:W422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31875,6 +31875,231 @@
         <v>349.41</v>
       </c>
       <c r="W419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="C420" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="D420" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="E420" t="n">
+        <v>333.43</v>
+      </c>
+      <c r="F420" t="n">
+        <v>329.87</v>
+      </c>
+      <c r="G420" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="H420" t="n">
+        <v>325.61</v>
+      </c>
+      <c r="I420" t="n">
+        <v>333.98</v>
+      </c>
+      <c r="J420" t="n">
+        <v>338.64</v>
+      </c>
+      <c r="K420" t="n">
+        <v>339.77</v>
+      </c>
+      <c r="L420" t="n">
+        <v>340.88</v>
+      </c>
+      <c r="M420" t="n">
+        <v>350.61</v>
+      </c>
+      <c r="N420" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="O420" t="n">
+        <v>353.11</v>
+      </c>
+      <c r="P420" t="n">
+        <v>363.87</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="R420" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="S420" t="n">
+        <v>342.56</v>
+      </c>
+      <c r="T420" t="n">
+        <v>343.71</v>
+      </c>
+      <c r="U420" t="n">
+        <v>346.07</v>
+      </c>
+      <c r="V420" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:53:30+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="C421" t="n">
+        <v>334.7</v>
+      </c>
+      <c r="D421" t="n">
+        <v>335.38</v>
+      </c>
+      <c r="E421" t="n">
+        <v>335.43</v>
+      </c>
+      <c r="F421" t="n">
+        <v>331.64</v>
+      </c>
+      <c r="G421" t="n">
+        <v>328.57</v>
+      </c>
+      <c r="H421" t="n">
+        <v>326.3</v>
+      </c>
+      <c r="I421" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="J421" t="n">
+        <v>338.11</v>
+      </c>
+      <c r="K421" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="L421" t="n">
+        <v>340.92</v>
+      </c>
+      <c r="M421" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="N421" t="n">
+        <v>349.54</v>
+      </c>
+      <c r="O421" t="n">
+        <v>354.35</v>
+      </c>
+      <c r="P421" t="n">
+        <v>364.14</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>363.02</v>
+      </c>
+      <c r="R421" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="S421" t="n">
+        <v>342.42</v>
+      </c>
+      <c r="T421" t="n">
+        <v>343.78</v>
+      </c>
+      <c r="U421" t="n">
+        <v>346.08</v>
+      </c>
+      <c r="V421" t="n">
+        <v>350.46</v>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>346.38</v>
+      </c>
+      <c r="C422" t="n">
+        <v>336</v>
+      </c>
+      <c r="D422" t="n">
+        <v>337.31</v>
+      </c>
+      <c r="E422" t="n">
+        <v>336.97</v>
+      </c>
+      <c r="F422" t="n">
+        <v>332.31</v>
+      </c>
+      <c r="G422" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="H422" t="n">
+        <v>326.45</v>
+      </c>
+      <c r="I422" t="n">
+        <v>333.82</v>
+      </c>
+      <c r="J422" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="K422" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="L422" t="n">
+        <v>340.89</v>
+      </c>
+      <c r="M422" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="N422" t="n">
+        <v>350.66</v>
+      </c>
+      <c r="O422" t="n">
+        <v>355.04</v>
+      </c>
+      <c r="P422" t="n">
+        <v>364.76</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="R422" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="S422" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="T422" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="U422" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="V422" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="W422" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31891,7 +32116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B421"/>
+  <dimension ref="A1:B424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36104,6 +36329,36 @@
       </c>
       <c r="B421" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -36272,28 +36527,28 @@
         <v>0.0723</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1799866732043864</v>
+        <v>0.1795056169357405</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1091568438247894</v>
+        <v>0.1103022718134153</v>
       </c>
       <c r="M2" t="n">
-        <v>3.155703632567634</v>
+        <v>3.140116256360141</v>
       </c>
       <c r="N2" t="n">
-        <v>15.18226953633944</v>
+        <v>15.08214627968961</v>
       </c>
       <c r="O2" t="n">
-        <v>3.896443190441693</v>
+        <v>3.883573905526919</v>
       </c>
       <c r="P2" t="n">
-        <v>340.5180185569606</v>
+        <v>340.5229678428992</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36350,28 +36605,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2159357069959709</v>
+        <v>0.2140578030005387</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.129637913542499</v>
+        <v>0.1295284132508907</v>
       </c>
       <c r="M3" t="n">
-        <v>3.42609864840288</v>
+        <v>3.410549155554826</v>
       </c>
       <c r="N3" t="n">
-        <v>17.97722184283602</v>
+        <v>17.8690194196483</v>
       </c>
       <c r="O3" t="n">
-        <v>4.239955405760303</v>
+        <v>4.227176293892685</v>
       </c>
       <c r="P3" t="n">
-        <v>330.1191203361214</v>
+        <v>330.1384851151265</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36428,28 +36683,28 @@
         <v>0.079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2305395705736926</v>
+        <v>0.2337486652915208</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.139326300418488</v>
+        <v>0.1445242164201682</v>
       </c>
       <c r="M4" t="n">
-        <v>3.475873355384862</v>
+        <v>3.464250813761624</v>
       </c>
       <c r="N4" t="n">
-        <v>18.85393937955913</v>
+        <v>18.76784531345773</v>
       </c>
       <c r="O4" t="n">
-        <v>4.342112317704268</v>
+        <v>4.332187128167218</v>
       </c>
       <c r="P4" t="n">
-        <v>327.046572219354</v>
+        <v>327.0134276572959</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36506,28 +36761,28 @@
         <v>0.0774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1784322875558835</v>
+        <v>0.1855866681787067</v>
       </c>
       <c r="J5" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07220018102537662</v>
+        <v>0.07835595177980914</v>
       </c>
       <c r="M5" t="n">
-        <v>3.829312060855708</v>
+        <v>3.835258433944003</v>
       </c>
       <c r="N5" t="n">
-        <v>23.4946296474305</v>
+        <v>23.50898189536401</v>
       </c>
       <c r="O5" t="n">
-        <v>4.847125916193069</v>
+        <v>4.848606180683683</v>
       </c>
       <c r="P5" t="n">
-        <v>325.5451825022535</v>
+        <v>325.4713172052648</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36584,28 +36839,28 @@
         <v>0.0835</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1803875830604989</v>
+        <v>0.1849605135996016</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07212699428555702</v>
+        <v>0.07656566317911839</v>
       </c>
       <c r="M6" t="n">
-        <v>4.035931064246518</v>
+        <v>4.027646494571146</v>
       </c>
       <c r="N6" t="n">
-        <v>24.03862956078897</v>
+        <v>23.94302698968676</v>
       </c>
       <c r="O6" t="n">
-        <v>4.902920513407184</v>
+        <v>4.893161247055605</v>
       </c>
       <c r="P6" t="n">
-        <v>323.2544941118576</v>
+        <v>323.2072791888755</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36662,28 +36917,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2185036050020338</v>
+        <v>0.2177393194474125</v>
       </c>
       <c r="J7" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08692775825086319</v>
+        <v>0.087767378085014</v>
       </c>
       <c r="M7" t="n">
-        <v>4.424154661648511</v>
+        <v>4.396837865522104</v>
       </c>
       <c r="N7" t="n">
-        <v>28.79848180372272</v>
+        <v>28.59533807571697</v>
       </c>
       <c r="O7" t="n">
-        <v>5.36642169454868</v>
+        <v>5.34746089987734</v>
       </c>
       <c r="P7" t="n">
-        <v>323.1013434669053</v>
+        <v>323.1092293903263</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36740,28 +36995,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.141632173078818</v>
+        <v>0.1356068705641079</v>
       </c>
       <c r="J8" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K8" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04354903359040418</v>
+        <v>0.04056559176982821</v>
       </c>
       <c r="M8" t="n">
-        <v>4.012137063288159</v>
+        <v>4.01706160017672</v>
       </c>
       <c r="N8" t="n">
-        <v>25.29960528905145</v>
+        <v>25.23886962296239</v>
       </c>
       <c r="O8" t="n">
-        <v>5.029871299452049</v>
+        <v>5.023830174574215</v>
       </c>
       <c r="P8" t="n">
-        <v>326.415884792824</v>
+        <v>326.4780673145209</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36818,28 +37073,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.225326393477696</v>
+        <v>0.2265324575710386</v>
       </c>
       <c r="J9" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K9" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1272179966926806</v>
+        <v>0.1303647508194929</v>
       </c>
       <c r="M9" t="n">
-        <v>3.416613137028984</v>
+        <v>3.396671896273266</v>
       </c>
       <c r="N9" t="n">
-        <v>20.0026290544356</v>
+        <v>19.86492217695308</v>
       </c>
       <c r="O9" t="n">
-        <v>4.47242988256223</v>
+        <v>4.457008209208626</v>
       </c>
       <c r="P9" t="n">
-        <v>326.9201033326889</v>
+        <v>326.9076567273357</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36896,28 +37151,28 @@
         <v>0.0864</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2152151012044038</v>
+        <v>0.217707804942012</v>
       </c>
       <c r="J10" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K10" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0711589450762834</v>
+        <v>0.07385162028960457</v>
       </c>
       <c r="M10" t="n">
-        <v>4.459494692459558</v>
+        <v>4.434603355154668</v>
       </c>
       <c r="N10" t="n">
-        <v>34.71867201439922</v>
+        <v>34.4919366839033</v>
       </c>
       <c r="O10" t="n">
-        <v>5.892255257064074</v>
+        <v>5.872983627076045</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8005880892281</v>
+        <v>330.7748634430561</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36974,28 +37229,28 @@
         <v>0.12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1453132334075272</v>
+        <v>0.1443060288111134</v>
       </c>
       <c r="J11" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K11" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02448922653395103</v>
+        <v>0.02457599443668068</v>
       </c>
       <c r="M11" t="n">
-        <v>5.40893798921046</v>
+        <v>5.376373553862618</v>
       </c>
       <c r="N11" t="n">
-        <v>48.30288317634973</v>
+        <v>47.96233623370539</v>
       </c>
       <c r="O11" t="n">
-        <v>6.950027566589196</v>
+        <v>6.925484548658338</v>
       </c>
       <c r="P11" t="n">
-        <v>336.2851367723118</v>
+        <v>336.2955357361539</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37052,28 +37307,28 @@
         <v>0.1196</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1456719807888098</v>
+        <v>0.1439920360467991</v>
       </c>
       <c r="J12" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K12" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02724676475816434</v>
+        <v>0.02709347613000124</v>
       </c>
       <c r="M12" t="n">
-        <v>5.207692248679277</v>
+        <v>5.181457640503014</v>
       </c>
       <c r="N12" t="n">
-        <v>43.50563509614486</v>
+        <v>43.20483697501638</v>
       </c>
       <c r="O12" t="n">
-        <v>6.595880160838647</v>
+        <v>6.573038640919159</v>
       </c>
       <c r="P12" t="n">
-        <v>338.1008564158026</v>
+        <v>338.1181954215107</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37130,28 +37385,28 @@
         <v>0.0833</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1746159569111581</v>
+        <v>0.1780460593125306</v>
       </c>
       <c r="J13" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K13" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04344255585056411</v>
+        <v>0.0458070884868137</v>
       </c>
       <c r="M13" t="n">
-        <v>4.835526852341088</v>
+        <v>4.811523910701717</v>
       </c>
       <c r="N13" t="n">
-        <v>38.63833268940625</v>
+        <v>38.40197940486004</v>
       </c>
       <c r="O13" t="n">
-        <v>6.215973993623706</v>
+        <v>6.196933064416626</v>
       </c>
       <c r="P13" t="n">
-        <v>343.9376806556459</v>
+        <v>343.9022969464625</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37208,28 +37463,28 @@
         <v>0.0706</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07716717231756907</v>
+        <v>0.08093564003405154</v>
       </c>
       <c r="J14" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K14" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009424046183649115</v>
+        <v>0.01052480491685026</v>
       </c>
       <c r="M14" t="n">
-        <v>4.711471846389621</v>
+        <v>4.688251764538049</v>
       </c>
       <c r="N14" t="n">
-        <v>36.02221232476324</v>
+        <v>35.81424902424708</v>
       </c>
       <c r="O14" t="n">
-        <v>6.001850741626556</v>
+        <v>5.984500733081004</v>
       </c>
       <c r="P14" t="n">
-        <v>345.1190514473177</v>
+        <v>345.0801744974493</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37286,28 +37541,28 @@
         <v>0.1594</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06182855156051358</v>
+        <v>0.06566216706440671</v>
       </c>
       <c r="J15" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K15" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007345823270332841</v>
+        <v>0.008408115977817765</v>
       </c>
       <c r="M15" t="n">
-        <v>4.237997993626879</v>
+        <v>4.224528758546639</v>
       </c>
       <c r="N15" t="n">
-        <v>29.72969659324261</v>
+        <v>29.56991491415375</v>
       </c>
       <c r="O15" t="n">
-        <v>5.452494529409691</v>
+        <v>5.437822626212973</v>
       </c>
       <c r="P15" t="n">
-        <v>349.8673061957436</v>
+        <v>349.8277535538033</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37364,28 +37619,28 @@
         <v>0.1171</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.01506601961097869</v>
+        <v>-0.009207697458424037</v>
       </c>
       <c r="J16" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K16" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0005774709533497013</v>
+        <v>0.0002185013469003794</v>
       </c>
       <c r="M16" t="n">
-        <v>3.814110330363254</v>
+        <v>3.811116222827115</v>
       </c>
       <c r="N16" t="n">
-        <v>22.55909990851417</v>
+        <v>22.51137892612702</v>
       </c>
       <c r="O16" t="n">
-        <v>4.749642082148314</v>
+        <v>4.744615782771774</v>
       </c>
       <c r="P16" t="n">
-        <v>360.6509140511771</v>
+        <v>360.59044353933</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37442,28 +37697,28 @@
         <v>0.0732</v>
       </c>
       <c r="I17" t="n">
-        <v>0.006129222252021204</v>
+        <v>0.01914350154465696</v>
       </c>
       <c r="J17" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K17" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L17" t="n">
-        <v>8.467436316128563e-05</v>
+        <v>0.0008219803235639533</v>
       </c>
       <c r="M17" t="n">
-        <v>4.173465183835679</v>
+        <v>4.199511139269465</v>
       </c>
       <c r="N17" t="n">
-        <v>25.47579496818386</v>
+        <v>25.85075575913982</v>
       </c>
       <c r="O17" t="n">
-        <v>5.047355244896465</v>
+        <v>5.084363849995378</v>
       </c>
       <c r="P17" t="n">
-        <v>353.9033348933417</v>
+        <v>353.7690004320975</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37520,28 +37775,28 @@
         <v>0.1014</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06200689095699856</v>
+        <v>0.07085523230488618</v>
       </c>
       <c r="J18" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K18" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01444845569459419</v>
+        <v>0.01879517961288435</v>
       </c>
       <c r="M18" t="n">
-        <v>3.279779918121055</v>
+        <v>3.298527826331647</v>
       </c>
       <c r="N18" t="n">
-        <v>15.06064406106815</v>
+        <v>15.20918996284816</v>
       </c>
       <c r="O18" t="n">
-        <v>3.880804563627</v>
+        <v>3.899896147700367</v>
       </c>
       <c r="P18" t="n">
-        <v>343.7903610104614</v>
+        <v>343.6990366559626</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37598,28 +37853,28 @@
         <v>0.1035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.086050965794028</v>
+        <v>0.09326420088727359</v>
       </c>
       <c r="J19" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K19" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02795589727266679</v>
+        <v>0.03287128803701611</v>
       </c>
       <c r="M19" t="n">
-        <v>3.185976037905985</v>
+        <v>3.197746769790606</v>
       </c>
       <c r="N19" t="n">
-        <v>14.8502428328242</v>
+        <v>14.91505343441239</v>
       </c>
       <c r="O19" t="n">
-        <v>3.853601280986942</v>
+        <v>3.862001221441079</v>
       </c>
       <c r="P19" t="n">
-        <v>335.0984780925565</v>
+        <v>335.0241376142303</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37676,28 +37931,28 @@
         <v>0.1228</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1899573370730178</v>
+        <v>0.1964104051300886</v>
       </c>
       <c r="J20" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K20" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L20" t="n">
-        <v>0.123680253846873</v>
+        <v>0.1320526227075738</v>
       </c>
       <c r="M20" t="n">
-        <v>3.164525105058069</v>
+        <v>3.174657208756569</v>
       </c>
       <c r="N20" t="n">
-        <v>14.74632831424647</v>
+        <v>14.77755753128976</v>
       </c>
       <c r="O20" t="n">
-        <v>3.840094831413213</v>
+        <v>3.844158884761368</v>
       </c>
       <c r="P20" t="n">
-        <v>334.1368986281275</v>
+        <v>334.0703905873602</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37754,28 +38009,28 @@
         <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3807444654427254</v>
+        <v>0.3873664559144382</v>
       </c>
       <c r="J21" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K21" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3428608712107286</v>
+        <v>0.3526259981678724</v>
       </c>
       <c r="M21" t="n">
-        <v>3.277656735386091</v>
+        <v>3.285797903041731</v>
       </c>
       <c r="N21" t="n">
-        <v>16.02566739621572</v>
+        <v>16.05507202373597</v>
       </c>
       <c r="O21" t="n">
-        <v>4.003207138809548</v>
+        <v>4.006878089452681</v>
       </c>
       <c r="P21" t="n">
-        <v>331.1426456171201</v>
+        <v>331.0743976635714</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37832,28 +38087,28 @@
         <v>0.1131</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3214839955044986</v>
+        <v>0.3303070997459644</v>
       </c>
       <c r="J22" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K22" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2390143464862075</v>
+        <v>0.2497793151386243</v>
       </c>
       <c r="M22" t="n">
-        <v>3.581694579784541</v>
+        <v>3.596404499417239</v>
       </c>
       <c r="N22" t="n">
-        <v>18.8963069111092</v>
+        <v>19.01592343453597</v>
       </c>
       <c r="O22" t="n">
-        <v>4.346988257530632</v>
+        <v>4.360725104215579</v>
       </c>
       <c r="P22" t="n">
-        <v>335.6005348086684</v>
+        <v>335.5094697260805</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37891,7 +38146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W419"/>
+  <dimension ref="A1:W422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86881,6 +87136,357 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-38.27446428187551,178.3304210723123</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-38.275161029098456,178.33062658109233</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-38.2758194531749,178.33094783456656</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-38.276480620650965,178.3312607829001</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-38.277151899009844,178.3315395150411</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-38.277816434954,178.3318303818158</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-38.27848913470994,178.33209683026823</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-38.27912763811511,178.33248134232517</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-38.279782672194216,178.33282818513646</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-38.28043903083659,178.33318548216045</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-38.28107025732227,178.33360114572162</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-38.28166316416559,178.33410195085446</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-38.2822528049748,178.33460548385358</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-38.28280349647977,178.33516657914222</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-38.28331209753478,178.3357821344014</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-38.28379314471193,178.3364262306909</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-38.284329325932184,178.3370263032214</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>-38.28487141622471,178.33760994684246</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>-38.285365942553824,178.33825824027016</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>-38.2857932822584,178.3389848716434</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>-38.286123916509624,178.33978707141708</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:53:30+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-38.27446087126317,178.33043137473382</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-38.275156295984864,178.3306408784538</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-38.2758138847684,178.33096465511784</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-38.27647366009711,178.33128180874823</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-38.27714580553751,178.33155815834786</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-38.277815466568406,178.33183345188914</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-38.278486876057386,178.33210415779308</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-38.27912839100602,178.33247889979975</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-38.27978452821874,178.33282261918058</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-38.2804397956905,178.33318354503436</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-38.281070084646444,178.33360154579356</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-38.281661846124265,178.33410453604682</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-38.282250780074385,178.33460883081847</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-38.282796646485544,178.33517773343817</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-38.2833104136505,178.33578435156414</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-38.283786837370464,178.33643283759844</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-38.284331802472416,178.33702366105481</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>-38.28487235183023,178.33760887922173</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>-38.28536545781129,178.33825874917406</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>-38.28579320638969,178.33898493279142</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>-38.28612273232488,178.33978788920078</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:53:38+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-38.27445568573872,178.33044703861754</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-38.27515177168359,178.33065454504742</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-38.27580716787509,178.33098494490403</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-38.27646830046828,178.33129799864832</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-38.27714349896815,178.3315652154179</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-38.277815232820146,178.33183419294133</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-38.2784863850459,178.33210575073323</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-38.279128161865316,178.33247964317707</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-38.27978400292881,178.33282419445115</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-38.28044112412092,178.33318018055215</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-38.281070214153324,178.3336012457396</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-38.281658526612546,178.33411104690117</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-38.2822446506456,178.33461896217042</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-38.282792834794805,178.3351839402632</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-38.28330654695311,178.33578944282635</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-38.283781153831725,178.33643879107453</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-38.28433008265282,178.33702549589273</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>-38.28487415621229,178.33760682023885</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>-38.285366496545315,178.33825765866564</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>-38.285795027238755,178.33898346523836</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>-38.28612399545526,178.33978701689819</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
